--- a/Dataset25.xlsx
+++ b/Dataset25.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/debdeeppaul/Documents/Procurement/PIDSG25/forecast25/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{433EC199-D42E-604D-9717-45B0B82C190C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC9143F-7124-B54D-B0B2-8565A8EC714B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="13900" xr2:uid="{39FACA68-203D-43F8-8009-A489CDDBDB68}"/>
   </bookViews>
@@ -212,17 +212,17 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4305,10 +4305,10 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="10"/>
+      <c r="C3" s="12"/>
       <c r="D3" s="2">
         <v>45383</v>
       </c>
@@ -4770,10 +4770,10 @@
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.2">
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="12"/>
       <c r="D14" s="2">
         <v>45748</v>
       </c>
@@ -5347,171 +5347,175 @@
       </c>
     </row>
     <row r="31" spans="2:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="10">
         <f>D22/D20</f>
         <v>1.4112121263157897</v>
       </c>
-      <c r="E31" s="12">
-        <f t="shared" ref="D31:E32" si="8">E22/E20</f>
+      <c r="E31" s="10">
+        <f t="shared" ref="E31:E32" si="8">E22/E20</f>
         <v>0</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="10">
         <f>F22/F20</f>
         <v>1.4239201846153846</v>
       </c>
-      <c r="G31" s="12">
+      <c r="G31" s="10">
         <f t="shared" ref="G31:P31" si="9">G22/G20</f>
         <v>1.3839971887850469</v>
       </c>
-      <c r="H31" s="12">
+      <c r="H31" s="10">
         <f t="shared" si="9"/>
         <v>1.3839971887850469</v>
       </c>
-      <c r="I31" s="12">
+      <c r="I31" s="10">
         <f t="shared" si="9"/>
         <v>1.1752992</v>
       </c>
-      <c r="J31" s="12">
+      <c r="J31" s="10">
         <f t="shared" si="9"/>
         <v>1.9485223578947368</v>
       </c>
-      <c r="K31" s="12">
+      <c r="K31" s="10">
         <f t="shared" si="9"/>
         <v>1.3721483749865089</v>
       </c>
-      <c r="L31" s="12">
+      <c r="L31" s="10">
         <f t="shared" si="9"/>
         <v>1.4011120072454315</v>
       </c>
-      <c r="M31" s="12">
+      <c r="M31" s="10">
         <f t="shared" si="9"/>
         <v>0.91670298893288649</v>
       </c>
-      <c r="N31" s="12">
+      <c r="N31" s="10">
         <f t="shared" si="9"/>
         <v>1.342483541986407</v>
       </c>
-      <c r="O31" s="12">
+      <c r="O31" s="10">
         <f t="shared" si="9"/>
         <v>1.3003157449840588</v>
       </c>
-      <c r="P31" s="12">
+      <c r="P31" s="10">
         <f t="shared" si="9"/>
         <v>1.3973793311188398</v>
       </c>
     </row>
     <row r="32" spans="2:16" ht="32" x14ac:dyDescent="0.2">
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="10">
         <f>D22/D19</f>
         <v>0.62067200000000011</v>
       </c>
-      <c r="E32" s="12">
+      <c r="E32" s="10">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="F32" s="12">
-        <f t="shared" ref="E32:O32" si="10">F22/F19</f>
+      <c r="F32" s="10">
+        <f t="shared" ref="F32:O32" si="10">F22/F19</f>
         <v>0.64274175</v>
       </c>
-      <c r="G32" s="12">
+      <c r="G32" s="10">
         <f t="shared" si="10"/>
         <v>0.64274175</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H32" s="10">
         <f t="shared" si="10"/>
         <v>0.64274175</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I32" s="10">
         <f t="shared" si="10"/>
         <v>0.64274175</v>
       </c>
-      <c r="J32" s="12">
+      <c r="J32" s="10">
         <f t="shared" si="10"/>
         <v>0.64274175</v>
       </c>
-      <c r="K32" s="12">
+      <c r="K32" s="10">
         <f t="shared" si="10"/>
         <v>0.64274175</v>
       </c>
-      <c r="L32" s="12">
+      <c r="L32" s="10">
         <f t="shared" si="10"/>
         <v>0.64274175</v>
       </c>
-      <c r="M32" s="12">
+      <c r="M32" s="10">
         <f t="shared" si="10"/>
         <v>0.64274175</v>
       </c>
-      <c r="N32" s="12">
+      <c r="N32" s="10">
         <f t="shared" si="10"/>
         <v>0.64274175</v>
       </c>
-      <c r="O32" s="12">
+      <c r="O32" s="10">
         <f t="shared" si="10"/>
         <v>0.64274175</v>
       </c>
-      <c r="P32" s="12"/>
+      <c r="P32" s="10"/>
     </row>
-    <row r="34" spans="3:15" ht="32" x14ac:dyDescent="0.2">
-      <c r="C34" s="11" t="s">
+    <row r="34" spans="3:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="C34" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="10">
         <f>D20/D19</f>
         <v>0.43981481481481483</v>
       </c>
-      <c r="E34" s="12" t="e">
+      <c r="E34" s="10" t="e">
         <f>E20/E19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="F34" s="12">
-        <f t="shared" ref="E34:O34" si="11">F20/F19</f>
+      <c r="F34" s="10">
+        <f t="shared" ref="F34:O34" si="11">F20/F19</f>
         <v>0.4513888888888889</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="10">
         <f t="shared" si="11"/>
         <v>0.46440972222222221</v>
       </c>
-      <c r="H34" s="12">
+      <c r="H34" s="10">
         <f t="shared" si="11"/>
         <v>0.46440972222222221</v>
       </c>
-      <c r="I34" s="12">
+      <c r="I34" s="10">
         <f t="shared" si="11"/>
         <v>0.546875</v>
       </c>
-      <c r="J34" s="12">
+      <c r="J34" s="10">
         <f t="shared" si="11"/>
         <v>0.3298611111111111</v>
       </c>
-      <c r="K34" s="12">
+      <c r="K34" s="10">
         <f t="shared" si="11"/>
         <v>0.46842000596788197</v>
       </c>
-      <c r="L34" s="12">
+      <c r="L34" s="10">
         <f t="shared" si="11"/>
         <v>0.45873687947591152</v>
       </c>
-      <c r="M34" s="12">
+      <c r="M34" s="10">
         <f t="shared" si="11"/>
         <v>0.70114503580729159</v>
       </c>
-      <c r="N34" s="12">
+      <c r="N34" s="10">
         <f t="shared" si="11"/>
         <v>0.47877067382812499</v>
       </c>
-      <c r="O34" s="12">
+      <c r="O34" s="10">
         <f t="shared" si="11"/>
         <v>0.49429667561848961</v>
       </c>
+      <c r="P34" s="10">
+        <f>AVERAGE(F34:O34)</f>
+        <v>0.48583137151421446</v>
+      </c>
     </row>
-    <row r="35" spans="3:15" ht="32" x14ac:dyDescent="0.2">
-      <c r="C35" s="11" t="s">
+    <row r="35" spans="3:16" ht="32" x14ac:dyDescent="0.2">
+      <c r="C35" s="9" t="s">
         <v>22</v>
       </c>
       <c r="D35">
@@ -5523,7 +5527,7 @@
         <v>0.63263490439887693</v>
       </c>
       <c r="F35">
-        <f t="shared" ref="E35:O35" si="12">F17/F21</f>
+        <f t="shared" ref="F35:O35" si="12">F17/F21</f>
         <v>0.61585128604658612</v>
       </c>
       <c r="G35">
@@ -5563,22 +5567,22 @@
         <v>0.58125037454157436</v>
       </c>
     </row>
-    <row r="45" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="3:16" x14ac:dyDescent="0.2">
       <c r="D45">
         <v>1.0353697749196142</v>
       </c>
     </row>
-    <row r="46" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="3:16" x14ac:dyDescent="0.2">
       <c r="D46">
         <v>1.0363344051446943</v>
       </c>
     </row>
-    <row r="47" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="3:16" x14ac:dyDescent="0.2">
       <c r="D47">
         <v>1.0372990353697749</v>
       </c>
     </row>
-    <row r="48" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="3:16" x14ac:dyDescent="0.2">
       <c r="D48">
         <v>1.0446945337620579</v>
       </c>
